--- a/Data/Home/BedroomTwo.Humidity.xlsx
+++ b/Data/Home/BedroomTwo.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709261749</v>
+        <v>1711843189</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,10 +502,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Dry</t>
+          <t>BedroomTwo.Humidity.state: Moist</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709270372</v>
+        <v>1711844063</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -529,10 +535,15 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
+          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709270851</v>
+        <v>1711845961</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709272542</v>
+        <v>1711848049</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +605,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709273759</v>
+        <v>1711862832</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709275558</v>
+        <v>1711888168</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709276843</v>
+        <v>1711928133</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709278781</v>
+        <v>1711929664</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +741,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709280038</v>
+        <v>1711930422</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +778,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709290402</v>
+        <v>1711931615</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +811,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709254302</v>
+        <v>1711938420</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709257273</v>
+        <v>1711969263</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709257783</v>
+        <v>1712025979</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709259514</v>
+        <v>1712055314</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +939,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709260703</v>
+        <v>1712112097</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +972,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709262348</v>
+        <v>1712139794</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1005,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709264219</v>
+        <v>1712197683</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1038,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709265337</v>
+        <v>1712225991</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1071,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709267174</v>
+        <v>1712284390</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1104,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709269628</v>
+        <v>1712314105</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1141,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1160,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709274850</v>
+        <v>1712378640</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1170,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709321008</v>
+        <v>1712402881</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1207,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1226,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709346756</v>
+        <v>1712456026</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1240,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1259,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709348635</v>
+        <v>1712456936</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1273,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709349956</v>
+        <v>1712535637</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1310,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709352042</v>
+        <v>1712538016</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1339,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709353372</v>
+        <v>1712551543</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1372,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709354830</v>
+        <v>1712574417</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1405,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709356776</v>
+        <v>1712622053</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1442,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709358043</v>
+        <v>1712622940</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1475,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709359994</v>
+        <v>1712624774</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1512,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709429626</v>
+        <v>1712626868</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1545,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709438912</v>
+        <v>1712630029</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1574,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1597,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709440280</v>
+        <v>1712705907</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1607,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1630,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709442470</v>
+        <v>1712706336</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1644,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1663,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709443813</v>
+        <v>1712707226</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1677,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709446000</v>
+        <v>1712708993</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1714,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709447365</v>
+        <v>1712711276</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1743,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709449969</v>
+        <v>1712716480</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1776,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709451054</v>
+        <v>1712750518</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1809,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1832,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709454938</v>
+        <v>1712792010</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1846,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1865,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709511924</v>
+        <v>1712792906</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1875,15 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
+          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709514885</v>
+        <v>1712794795</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1916,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1935,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709516136</v>
+        <v>1712797245</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1945,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1968,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709518013</v>
+        <v>1712802844</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1978,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2001,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709519400</v>
+        <v>1712831111</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2011,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2034,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709521160</v>
+        <v>1712887502</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2044,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2067,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709522500</v>
+        <v>1712917844</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2077,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2100,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709524376</v>
+        <v>1712973683</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2114,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2133,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709525697</v>
+        <v>1712977964</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2143,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2166,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709527420</v>
+        <v>1712982714</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2176,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2199,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709531287</v>
+        <v>1713007122</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2213,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2232,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709553097</v>
+        <v>1713061049</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2242,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2265,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709599709</v>
+        <v>1713090112</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2279,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2298,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709616227</v>
+        <v>1713138205</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2312,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709617435</v>
+        <v>1713139083</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2345,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2368,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709619484</v>
+        <v>1713140871</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2382,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2401,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709620755</v>
+        <v>1713142993</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2411,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2434,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709624101</v>
+        <v>1713156465</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2444,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2467,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709625045</v>
+        <v>1713179963</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2477,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2500,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709634012</v>
+        <v>1713224639</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2514,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2533,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709713357</v>
+        <v>1713225523</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2547,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2570,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709771008</v>
+        <v>1713227016</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2584,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2603,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709791555</v>
+        <v>1713228059</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2613,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2636,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709856427</v>
+        <v>1713230110</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2646,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2669,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709870455</v>
+        <v>1713236183</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2679,15 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2706,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709872539</v>
+        <v>1713236435</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2716,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2739,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709873540</v>
+        <v>1713236779</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2749,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2772,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709875382</v>
+        <v>1713237505</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2786,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2805,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709876143</v>
+        <v>1713243073</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2815,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2838,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709882867</v>
+        <v>1713243797</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2852,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2871,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709948588</v>
+        <v>1713251674</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2885,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2904,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709950692</v>
+        <v>1713252386</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2918,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2937,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709951884</v>
+        <v>1713259423</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2947,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2970,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709953668</v>
+        <v>1713260139</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2984,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3003,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709954917</v>
+        <v>1713264148</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3013,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3036,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709956813</v>
+        <v>1713265289</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3050,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709958151</v>
+        <v>1713272203</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3083,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3106,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709959962</v>
+        <v>1713272916</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3120,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3139,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709961294</v>
+        <v>1713277248</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3153,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3176,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709964740</v>
+        <v>1713278026</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3190,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3209,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710032071</v>
+        <v>1713282993</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3219,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
+          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3246,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710039135</v>
+        <v>1713283758</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3260,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3279,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710040404</v>
+        <v>1713288421</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3293,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3316,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710042435</v>
+        <v>1713289157</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3330,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3349,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710043760</v>
+        <v>1713283813</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3363,11 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3386,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710045961</v>
+        <v>1713315000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3400,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3419,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710047268</v>
+        <v>1713316196</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3429,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3452,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710049298</v>
+        <v>1713318576</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3462,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3485,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710050639</v>
+        <v>1713322284</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3495,15 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3522,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710054110</v>
+        <v>1713322533</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3532,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3555,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710117973</v>
+        <v>1713322868</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3569,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3588,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710133131</v>
+        <v>1713323557</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3602,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3621,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710134460</v>
+        <v>1713351275</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3635,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3658,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710136364</v>
+        <v>1713352081</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3672,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3691,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710137449</v>
+        <v>1713354960</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3705,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3728,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710151931</v>
+        <v>1713355806</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3742,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3761,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710211154</v>
+        <v>1713356970</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3775,11 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3798,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710213875</v>
+        <v>1713399703</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3812,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3831,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710215170</v>
+        <v>1713400868</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3841,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3864,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710217071</v>
+        <v>1713403137</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3874,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3897,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710218420</v>
+        <v>1713415761</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3907,15 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3934,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710220272</v>
+        <v>1713416020</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3944,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3967,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710221649</v>
+        <v>1713416359</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3977,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4000,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710223486</v>
+        <v>1713417018</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4014,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4033,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710293444</v>
+        <v>1713435874</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4047,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4066,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710305968</v>
+        <v>1713436584</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4080,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4099,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710322475</v>
+        <v>1713440260</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4113,11 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4136,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710373599</v>
+        <v>1713441078</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4150,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4169,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710467274</v>
+        <v>1713442783</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4179,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
+          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4206,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710473596</v>
+        <v>1713488158</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4220,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710474830</v>
+        <v>1713489343</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4249,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4272,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710476692</v>
+        <v>1713491661</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4282,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4305,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710477871</v>
+        <v>1713494364</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4315,15 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4342,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710479766</v>
+        <v>1713494626</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4352,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4375,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710480906</v>
+        <v>1713494955</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4385,11 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4408,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710482825</v>
+        <v>1713495642</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4422,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4441,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710484013</v>
+        <v>1713506870</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4451,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4474,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710485956</v>
+        <v>1713507547</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4488,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4507,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710562312</v>
+        <v>1713529364</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4521,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4544,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710566087</v>
+        <v>1713530130</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4558,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4577,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710567083</v>
+        <v>1713533863</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4591,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4614,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710633660</v>
+        <v>1713534566</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4628,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4647,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710643474</v>
+        <v>1713539339</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4661,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4684,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710645729</v>
+        <v>1713540036</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4698,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4717,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710646772</v>
+        <v>1713542769</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4731,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4754,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710648987</v>
+        <v>1713577110</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4768,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4787,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710650040</v>
+        <v>1713578141</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4801,11 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4824,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710652239</v>
+        <v>1713660204</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4838,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4857,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710653296</v>
+        <v>1713741069</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4867,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4890,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710655566</v>
+        <v>1713746040</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4900,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4923,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710656347</v>
+        <v>1713752528</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4933,15 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4960,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710674638</v>
+        <v>1713752782</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4970,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4993,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710723789</v>
+        <v>1713753118</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +5007,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5026,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710726135</v>
+        <v>1713753762</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5040,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5059,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710727992</v>
+        <v>1713782177</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5073,11 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5096,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710729053</v>
+        <v>1713783040</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5110,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5129,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710730916</v>
+        <v>1713786826</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5143,11 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5166,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710731993</v>
+        <v>1713787700</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5180,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5199,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710733932</v>
+        <v>1713789999</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5213,11 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5236,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710735008</v>
+        <v>1713833551</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5250,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5269,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710737057</v>
+        <v>1713834681</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5279,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5302,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710738119</v>
+        <v>1713836905</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5312,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5335,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710754301</v>
+        <v>1713839113</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5345,15 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5372,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710810233</v>
+        <v>1713839374</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5382,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5405,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710815688</v>
+        <v>1713839724</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5415,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5438,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710819957</v>
+        <v>1713840438</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5452,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5471,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710821048</v>
+        <v>1713848424</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5481,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5504,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710825652</v>
+        <v>1713849117</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5518,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5537,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710826733</v>
+        <v>1713867499</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5551,11 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5574,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710830690</v>
+        <v>1713868405</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5588,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5607,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710835591</v>
+        <v>1713871404</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5621,11 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5644,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710841480</v>
+        <v>1713872145</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5658,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5677,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710894287</v>
+        <v>1713875700</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5687,15 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
+          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5714,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710901082</v>
+        <v>1713876424</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5728,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5747,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710919148</v>
+        <v>1713877639</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5761,11 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5784,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711014695</v>
+        <v>1713879191</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5798,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5817,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711070026</v>
+        <v>1713880755</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5831,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5850,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711075900</v>
+        <v>1713881486</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5864,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5883,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711077238</v>
+        <v>1713889019</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5897,11 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5920,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711079325</v>
+        <v>1713917813</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5934,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5953,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711080495</v>
+        <v>1713918933</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5963,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5986,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711082614</v>
+        <v>1713921204</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5996,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +6019,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711083844</v>
+        <v>1713933543</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +6029,15 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6056,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711086054</v>
+        <v>1713933798</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6066,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6089,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711087486</v>
+        <v>1713934138</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +6099,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6122,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711089804</v>
+        <v>1713934830</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6136,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6155,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711154494</v>
+        <v>1713941850</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6169,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6188,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711161033</v>
+        <v>1713942591</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6202,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6221,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711162829</v>
+        <v>1713949918</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6231,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6254,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711163915</v>
+        <v>1713950651</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6268,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6287,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711165804</v>
+        <v>1713963908</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6301,11 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6324,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711166866</v>
+        <v>1714006390</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6338,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6357,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711168710</v>
+        <v>1714007484</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6367,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6390,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711170141</v>
+        <v>1714009637</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6400,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6423,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711171115</v>
+        <v>1714042698</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6097,10 +6433,11 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6456,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711173105</v>
+        <v>1714098441</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6466,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6489,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711179226</v>
+        <v>1714128768</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6499,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
+          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6522,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711189555</v>
+        <v>1714186525</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6532,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
+          <t>BedroomTwo.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6555,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711245274</v>
+        <v>1714215626</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,1030 +6569,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1711258266</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1711259522</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>1711261578</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>1711262961</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1711264963</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>1711266018</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1711296114</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>1711330339</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1711339318</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>1711340637</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1711342632</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>1711344027</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>1711346062</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>1711347407</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>1711350727</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>1711351734</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>1711367932</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>1711421206</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>1711435866</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>1711437462</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>1711438520</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>1711440017</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>1711441289</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>1711442822</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>1711444111</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>1711445622</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>1711446829</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>1711448297</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1711449575</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>1711450514</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1711465854</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>1711629677</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>BedroomTwo.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
